--- a/Bandra_September_2026_Reports_Data.xlsx
+++ b/Bandra_September_2026_Reports_Data.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Sales" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Classes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Instructors" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1 Sales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2 Classes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3 Instructors" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,13 +573,13 @@
         <v/>
       </c>
       <c r="C7" s="6" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-2.29</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="8">
@@ -611,13 +611,13 @@
         <v/>
       </c>
       <c r="C9" s="6" t="n">
-        <v>7178</v>
+        <v>7903</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>7180</v>
+        <v>7803</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.04</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="10">
@@ -652,7 +652,7 @@
         <v/>
       </c>
       <c r="D11" s="6" t="n">
-        <v>163708.75</v>
+        <v>145208.75</v>
       </c>
       <c r="E11" s="6" t="n">
         <v/>
@@ -1107,7 +1107,7 @@
         <v>489262.8</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>216525.94</v>
+        <v>214755.94</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>42480</v>
@@ -1135,7 +1135,7 @@
         <v>455913.17</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>130271.95</v>
+        <v>128501.95</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>58410</v>
@@ -1219,7 +1219,7 @@
         <v>478495.06</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>125275</v>
+        <v>123700</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>55125</v>
@@ -1247,7 +1247,7 @@
         <v>324402.77</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>94499.94</v>
+        <v>91349.94</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>36225.01</v>
@@ -1331,7 +1331,7 @@
         <v>448543.01</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>148037.5</v>
+        <v>146200</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>79012.5</v>
@@ -1415,7 +1415,7 @@
         <v>574574.71</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>110998.13</v>
+        <v>109160.63</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>58800</v>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="C131" s="6" t="n">
         <v>662243.04</v>
@@ -3234,13 +3234,13 @@
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C133" s="6" t="n">
         <v>327891</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>53380</v>
+        <v>34880</v>
       </c>
     </row>
     <row r="134">
@@ -4041,7 +4041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O206"/>
+  <dimension ref="A1:P206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4059,6 +4059,7 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4081,6 +4082,7 @@
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
       <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -4102,6 +4104,7 @@
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -4119,6 +4122,7 @@
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -4203,6 +4207,11 @@
           <t>lc_rate</t>
         </is>
       </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>show</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4250,7 +4259,10 @@
         <v>8</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>11.87</v>
+        <v>13.47</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>86.31999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -4299,7 +4311,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>9.539999999999999</v>
+        <v>10.54</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>89.45999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -4348,7 +4363,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>13.65</v>
+        <v>15.81</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>84.19</v>
       </c>
     </row>
     <row r="9">
@@ -4397,7 +4415,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>9.43</v>
+        <v>10.42</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>89.58</v>
       </c>
     </row>
     <row r="10">
@@ -4446,7 +4467,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>9.9</v>
+        <v>10.99</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>89.01000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -4495,7 +4519,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>12.05</v>
+        <v>13.7</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>86.3</v>
       </c>
     </row>
     <row r="12">
@@ -4544,7 +4571,10 @@
         <v>1</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>6.38</v>
+        <v>6.82</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>93.18000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -4593,7 +4623,10 @@
         <v>0</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>9.68</v>
+        <v>10.71</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>89.29000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -4642,7 +4675,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>17.65</v>
+        <v>21.43</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>78.56999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -4693,6 +4729,9 @@
       <c r="O15" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="P15" s="6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4742,6 +4781,9 @@
       <c r="O16" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="P16" s="6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4789,6 +4831,9 @@
         <v>1</v>
       </c>
       <c r="O17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="P17" s="6" t="n">
         <v/>
       </c>
     </row>
@@ -9035,149 +9080,149 @@
         </is>
       </c>
       <c r="B189" s="6" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C189" s="6" t="n">
-        <v>31.58</v>
+        <v>32.53</v>
       </c>
       <c r="D189" s="6" t="n">
-        <v>10369.36</v>
+        <v>10098.87</v>
       </c>
       <c r="E189" s="6" t="n">
-        <v>6.86</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>Enquiry on call</t>
+          <t>Social - Instagram</t>
         </is>
       </c>
       <c r="B190" s="6" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="C190" s="6" t="n">
-        <v>30.3</v>
+        <v>31.58</v>
       </c>
       <c r="D190" s="6" t="n">
-        <v>12678.38</v>
+        <v>6322.58</v>
       </c>
       <c r="E190" s="6" t="n">
-        <v>8.98</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>Social - Instagram</t>
+          <t>Enquiry on call</t>
         </is>
       </c>
       <c r="B191" s="6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C191" s="6" t="n">
-        <v>26.09</v>
+        <v>30.77</v>
       </c>
       <c r="D191" s="6" t="n">
-        <v>7439.09</v>
+        <v>12711.89</v>
       </c>
       <c r="E191" s="6" t="n">
-        <v>7.52</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>Website Form</t>
+          <t>Staff Referral</t>
         </is>
       </c>
       <c r="B192" s="6" t="n">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="C192" s="6" t="n">
-        <v>25.56</v>
+        <v>28.57</v>
       </c>
       <c r="D192" s="6" t="n">
-        <v>8280.200000000001</v>
+        <v>5423.21</v>
       </c>
       <c r="E192" s="6" t="n">
-        <v>6.65</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>Client Referral</t>
+          <t>Website Form</t>
         </is>
       </c>
       <c r="B193" s="6" t="n">
-        <v>256</v>
+        <v>130</v>
       </c>
       <c r="C193" s="6" t="n">
-        <v>23.83</v>
+        <v>26.15</v>
       </c>
       <c r="D193" s="6" t="n">
-        <v>6152.37</v>
+        <v>8154.1</v>
       </c>
       <c r="E193" s="6" t="n">
-        <v>5.25</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>Staff Referral</t>
+          <t>Client Referral</t>
         </is>
       </c>
       <c r="B194" s="6" t="n">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="C194" s="6" t="n">
-        <v>23.53</v>
+        <v>24.3</v>
       </c>
       <c r="D194" s="6" t="n">
-        <v>4775</v>
+        <v>5854.97</v>
       </c>
       <c r="E194" s="6" t="n">
-        <v>4.29</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>Outdoor Class</t>
+          <t>Abandoned checkout</t>
         </is>
       </c>
       <c r="B195" s="6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C195" s="6" t="n">
-        <v>9.09</v>
+        <v>10.53</v>
       </c>
       <c r="D195" s="6" t="n">
-        <v>143.18</v>
+        <v>1971.89</v>
       </c>
       <c r="E195" s="6" t="n">
-        <v>1.55</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>Abandoned checkout</t>
+          <t>Outdoor Class</t>
         </is>
       </c>
       <c r="B196" s="6" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C196" s="6" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="D196" s="6" t="n">
-        <v>1628.96</v>
+        <v>157.5</v>
       </c>
       <c r="E196" s="6" t="n">
-        <v>2.78</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="197">
@@ -9187,16 +9232,16 @@
         </is>
       </c>
       <c r="B197" s="6" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C197" s="6" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>924.05</v>
+        <v>898.13</v>
       </c>
       <c r="E197" s="6" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="199">
@@ -9225,7 +9270,7 @@
         </is>
       </c>
       <c r="B201" s="6" t="n">
-        <v>1110</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="202">
@@ -9235,7 +9280,7 @@
         </is>
       </c>
       <c r="B202" s="6" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="203">
@@ -9245,7 +9290,7 @@
         </is>
       </c>
       <c r="B203" s="6" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="204">
@@ -9255,7 +9300,7 @@
         </is>
       </c>
       <c r="B204" s="6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="205">
@@ -9275,7 +9320,7 @@
         </is>
       </c>
       <c r="B206" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -9289,7 +9334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U390"/>
+  <dimension ref="A1:V390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9306,13 +9351,14 @@
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9341,6 +9387,7 @@
       <c r="S1" s="2" t="n"/>
       <c r="T1" s="2" t="n"/>
       <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -9368,6 +9415,7 @@
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="2" t="n"/>
       <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -9391,6 +9439,7 @@
       <c r="S3" s="2" t="n"/>
       <c r="T3" s="2" t="n"/>
       <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -9472,35 +9521,40 @@
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
+          <t>show</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
           <t>share_sessions</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>share_att</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>s25</t>
         </is>
       </c>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>a25</t>
         </is>
       </c>
-      <c r="S5" s="5" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>r25</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr">
+      <c r="U5" s="5" t="inlineStr">
         <is>
           <t>d_sessions</t>
         </is>
       </c>
-      <c r="U5" s="5" t="inlineStr">
+      <c r="V5" s="5" t="inlineStr">
         <is>
           <t>d_att</t>
         </is>
@@ -9549,27 +9603,30 @@
         <v>997.74</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>11.9</v>
+        <v>13.5</v>
       </c>
       <c r="O6" s="6" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="P6" s="6" t="n">
         <v>15.06</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>14.6</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="R6" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="6" t="n">
         <v>233</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="T6" s="6" t="n">
         <v>141978.63</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="U6" s="6" t="n">
+      <c r="V6" s="6" t="n">
         <v>-28</v>
       </c>
     </row>
@@ -9616,27 +9673,30 @@
         <v>858.4</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>12.45</v>
+        <v>14.23</v>
       </c>
       <c r="O7" s="6" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="P7" s="6" t="n">
         <v>10.42</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="6" t="n">
         <v>14.6</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="R7" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="6" t="n">
         <v>145</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="T7" s="6" t="n">
         <v>80339.89</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="U7" s="6" t="n">
+      <c r="V7" s="6" t="n">
         <v>60</v>
       </c>
     </row>
@@ -9683,27 +9743,30 @@
         <v>783.27</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>5.91</v>
+        <v>6.29</v>
       </c>
       <c r="O8" s="6" t="n">
+        <v>93.70999999999999</v>
+      </c>
+      <c r="P8" s="6" t="n">
         <v>11.97</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>11.68</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="R8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="T8" s="6" t="n">
         <v>27584.75</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="U8" s="6" t="n">
+      <c r="V8" s="6" t="n">
         <v>134</v>
       </c>
     </row>
@@ -9750,27 +9813,30 @@
         <v>1026.84</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>7.8</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="O9" s="6" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="P9" s="6" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="6" t="n">
         <v>8.48</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="R9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="S9" s="6" t="n">
+      <c r="T9" s="6" t="n">
         <v>25854.1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="U9" s="6" t="n">
+      <c r="V9" s="6" t="n">
         <v>89</v>
       </c>
     </row>
@@ -9817,27 +9883,30 @@
         <v>829.77</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>10.92</v>
+        <v>12.26</v>
       </c>
       <c r="O10" s="6" t="n">
+        <v>87.73999999999999</v>
+      </c>
+      <c r="P10" s="6" t="n">
         <v>6.56</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="6" t="n">
         <v>9.69</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="R10" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="T10" s="6" t="n">
         <v>42108.01</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="U10" s="6" t="n">
+      <c r="V10" s="6" t="n">
         <v>64</v>
       </c>
     </row>
@@ -9884,27 +9953,30 @@
         <v>1058.28</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>13.43</v>
+        <v>15.52</v>
       </c>
       <c r="O11" s="6" t="n">
+        <v>84.48</v>
+      </c>
+      <c r="P11" s="6" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="6" t="n">
         <v>6.98</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="R11" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="6" t="n">
         <v>202</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="T11" s="6" t="n">
         <v>126571.85</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="6" t="n">
         <v>-14</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="V11" s="6" t="n">
         <v>-104</v>
       </c>
     </row>
@@ -9951,27 +10023,30 @@
         <v>875.54</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>13.48</v>
+        <v>15.57</v>
       </c>
       <c r="O12" s="6" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="P12" s="6" t="n">
         <v>10.04</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="6" t="n">
         <v>7.34</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="R12" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="6" t="n">
         <v>151</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="T12" s="6" t="n">
         <v>94777.95</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="6" t="n">
         <v>-2</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="V12" s="6" t="n">
         <v>-48</v>
       </c>
     </row>
@@ -10018,27 +10093,30 @@
         <v>849.28</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>15.44</v>
+        <v>18.26</v>
       </c>
       <c r="O13" s="6" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="P13" s="6" t="n">
         <v>4.63</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="6" t="n">
         <v>6.7</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="R13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="S13" s="6" t="n">
+      <c r="T13" s="6" t="n">
         <v>21136</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="V13" s="6" t="n">
         <v>38</v>
       </c>
     </row>
@@ -10085,27 +10163,30 @@
         <v>1021.53</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>8.6</v>
+        <v>9.41</v>
       </c>
       <c r="O14" s="6" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="P14" s="6" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="6" t="n">
         <v>5.41</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="R14" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="T14" s="6" t="n">
         <v>33279.1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="V14" s="6" t="n">
         <v>48</v>
       </c>
     </row>
@@ -10152,27 +10233,30 @@
         <v>1041.29</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>11.43</v>
+        <v>12.9</v>
       </c>
       <c r="O15" s="6" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="P15" s="6" t="n">
         <v>3.47</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="6" t="n">
         <v>3.85</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="R15" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="6" t="n">
         <v>204</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="T15" s="6" t="n">
         <v>142367.2</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="6" t="n">
         <v>-21</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="V15" s="6" t="n">
         <v>-150</v>
       </c>
     </row>
@@ -10219,27 +10303,30 @@
         <v>1023.33</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O16" s="6" t="n">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="P16" s="6" t="n">
         <v>4.25</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="6" t="n">
         <v>3.56</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="R16" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="T16" s="6" t="n">
         <v>71326.7</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="6" t="n">
         <v>-13</v>
       </c>
-      <c r="U16" s="6" t="n">
+      <c r="V16" s="6" t="n">
         <v>-42</v>
       </c>
     </row>
@@ -10286,27 +10373,30 @@
         <v>1007.98</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>12.9</v>
+        <v>14.81</v>
       </c>
       <c r="O17" s="6" t="n">
+        <v>85.19</v>
+      </c>
+      <c r="P17" s="6" t="n">
         <v>4.63</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="6" t="n">
         <v>3.28</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="R17" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="T17" s="6" t="n">
         <v>42830.96</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="V17" s="6" t="n">
         <v>-7</v>
       </c>
     </row>
@@ -10353,27 +10443,30 @@
         <v>938.55</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>10.64</v>
+        <v>11.9</v>
       </c>
       <c r="O18" s="6" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="P18" s="6" t="n">
         <v>2.32</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="6" t="n">
         <v>2.64</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="R18" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="S18" s="6" t="n">
+      <c r="T18" s="6" t="n">
         <v>78680.58</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="6" t="n">
         <v>-19</v>
       </c>
-      <c r="U18" s="6" t="n">
+      <c r="V18" s="6" t="n">
         <v>-61</v>
       </c>
     </row>
@@ -10420,27 +10513,30 @@
         <v>1329.21</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>13.04</v>
+        <v>15</v>
       </c>
       <c r="O19" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="P19" s="6" t="n">
         <v>1.54</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="6" t="n">
         <v>1.21</v>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="R19" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="S19" s="6" t="n">
+      <c r="T19" s="6" t="n">
         <v>3570.3</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="6" t="n">
         <v>-2</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="V19" s="6" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10496,18 +10592,21 @@
         <v>0</v>
       </c>
       <c r="Q20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="S20" s="6" t="n">
+      <c r="T20" s="6" t="n">
         <v>4560.85</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="6" t="n">
         <v>-2</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="V20" s="6" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -10563,18 +10662,21 @@
         <v>0</v>
       </c>
       <c r="Q21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="T21" s="6" t="n">
         <v>29319.29</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="6" t="n">
         <v>-8</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="V21" s="6" t="n">
         <v>-46</v>
       </c>
     </row>
@@ -10630,18 +10732,21 @@
         <v>0</v>
       </c>
       <c r="Q22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="S22" s="6" t="n">
+      <c r="T22" s="6" t="n">
         <v>15167.02</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="6" t="n">
         <v>-10</v>
       </c>
-      <c r="U22" s="6" t="n">
+      <c r="V22" s="6" t="n">
         <v>-26</v>
       </c>
     </row>
@@ -16041,19 +16146,19 @@
         </is>
       </c>
       <c r="B196" s="6" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C196" s="6" t="n">
         <v>31</v>
       </c>
       <c r="D196" s="6" t="n">
-        <v>9527.16</v>
+        <v>7731.68</v>
       </c>
       <c r="E196" s="6" t="n">
-        <v>9.83</v>
+        <v>6.98</v>
       </c>
       <c r="F196" s="6" t="n">
-        <v>21.99</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="197">
@@ -16063,19 +16168,19 @@
         </is>
       </c>
       <c r="B197" s="6" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C197" s="6" t="n">
         <v>13</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>4652.94</v>
+        <v>4934.94</v>
       </c>
       <c r="E197" s="6" t="n">
-        <v>4.16</v>
+        <v>4.24</v>
       </c>
       <c r="F197" s="6" t="n">
-        <v>18.57</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="198">
@@ -16085,19 +16190,19 @@
         </is>
       </c>
       <c r="B198" s="6" t="n">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="C198" s="6" t="n">
         <v>94</v>
       </c>
       <c r="D198" s="6" t="n">
-        <v>8984.48</v>
+        <v>8994.940000000001</v>
       </c>
       <c r="E198" s="6" t="n">
-        <v>7.6</v>
+        <v>7.44</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>27.57</v>
+        <v>28.48</v>
       </c>
     </row>
     <row r="199">
@@ -16129,19 +16234,19 @@
         </is>
       </c>
       <c r="B200" s="6" t="n">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="C200" s="6" t="n">
         <v>86</v>
       </c>
       <c r="D200" s="6" t="n">
-        <v>8983.540000000001</v>
+        <v>9286.389999999999</v>
       </c>
       <c r="E200" s="6" t="n">
-        <v>7.28</v>
+        <v>7.39</v>
       </c>
       <c r="F200" s="6" t="n">
-        <v>19.95</v>
+        <v>20.67</v>
       </c>
     </row>
     <row r="201">
@@ -16173,16 +16278,16 @@
         </is>
       </c>
       <c r="B202" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C202" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>252.86</v>
+        <v>295</v>
       </c>
       <c r="E202" s="6" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="F202" s="6" t="n">
         <v>0</v>
@@ -16195,19 +16300,19 @@
         </is>
       </c>
       <c r="B203" s="6" t="n">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="C203" s="6" t="n">
         <v>138</v>
       </c>
       <c r="D203" s="6" t="n">
-        <v>9733.52</v>
+        <v>9583.51</v>
       </c>
       <c r="E203" s="6" t="n">
-        <v>7.48</v>
+        <v>7.29</v>
       </c>
       <c r="F203" s="6" t="n">
-        <v>27.99</v>
+        <v>28.45</v>
       </c>
     </row>
     <row r="204">
@@ -16217,19 +16322,19 @@
         </is>
       </c>
       <c r="B204" s="6" t="n">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="C204" s="6" t="n">
         <v>102</v>
       </c>
       <c r="D204" s="6" t="n">
-        <v>10104.72</v>
+        <v>9668.200000000001</v>
       </c>
       <c r="E204" s="6" t="n">
-        <v>8.529999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>22.87</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="205">
@@ -16239,19 +16344,19 @@
         </is>
       </c>
       <c r="B205" s="6" t="n">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="C205" s="6" t="n">
         <v>69</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>10977.24</v>
+        <v>11322.14</v>
       </c>
       <c r="E205" s="6" t="n">
-        <v>10.33</v>
+        <v>10.18</v>
       </c>
       <c r="F205" s="6" t="n">
-        <v>24.3</v>
+        <v>25.27</v>
       </c>
     </row>
     <row r="206">
@@ -16261,19 +16366,19 @@
         </is>
       </c>
       <c r="B206" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C206" s="6" t="n">
         <v>12</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>25982.05</v>
+        <v>26615.76</v>
       </c>
       <c r="E206" s="6" t="n">
-        <v>29.29</v>
+        <v>29.98</v>
       </c>
       <c r="F206" s="6" t="n">
-        <v>28.57</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="207">
@@ -16283,19 +16388,19 @@
         </is>
       </c>
       <c r="B207" s="6" t="n">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C207" s="6" t="n">
         <v>48</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>8289.129999999999</v>
+        <v>8554.08</v>
       </c>
       <c r="E207" s="6" t="n">
-        <v>10.34</v>
+        <v>10.51</v>
       </c>
       <c r="F207" s="6" t="n">
-        <v>21.24</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="208">
@@ -16327,19 +16432,19 @@
         </is>
       </c>
       <c r="B209" s="6" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C209" s="6" t="n">
         <v>76</v>
       </c>
       <c r="D209" s="6" t="n">
-        <v>7310.09</v>
+        <v>6942.11</v>
       </c>
       <c r="E209" s="6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F209" s="6" t="n">
-        <v>20.88</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="210">
@@ -16349,19 +16454,19 @@
         </is>
       </c>
       <c r="B210" s="6" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C210" s="6" t="n">
         <v>63</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>9703.5</v>
+        <v>9826.17</v>
       </c>
       <c r="E210" s="6" t="n">
-        <v>7.67</v>
+        <v>7.7</v>
       </c>
       <c r="F210" s="6" t="n">
-        <v>23.86</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="211">
@@ -16371,19 +16476,19 @@
         </is>
       </c>
       <c r="B211" s="6" t="n">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C211" s="6" t="n">
         <v>69</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>6216.16</v>
+        <v>6343.39</v>
       </c>
       <c r="E211" s="6" t="n">
-        <v>5.26</v>
+        <v>5.29</v>
       </c>
       <c r="F211" s="6" t="n">
-        <v>22.77</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="212">
@@ -16415,19 +16520,19 @@
         </is>
       </c>
       <c r="B213" s="6" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C213" s="6" t="n">
         <v>15</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>3708.03</v>
+        <v>3511.73</v>
       </c>
       <c r="E213" s="6" t="n">
-        <v>3.39</v>
+        <v>3.18</v>
       </c>
       <c r="F213" s="6" t="n">
-        <v>18.75</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="214">
@@ -16437,19 +16542,19 @@
         </is>
       </c>
       <c r="B214" s="6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C214" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>9793.07</v>
+        <v>10576.52</v>
       </c>
       <c r="E214" s="6" t="n">
-        <v>7.07</v>
+        <v>7.4</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>22.22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="215">
@@ -16459,19 +16564,19 @@
         </is>
       </c>
       <c r="B215" s="6" t="n">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="C215" s="6" t="n">
         <v>107</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>8788.59</v>
+        <v>8663.33</v>
       </c>
       <c r="E215" s="6" t="n">
-        <v>8.01</v>
+        <v>7.49</v>
       </c>
       <c r="F215" s="6" t="n">
-        <v>20.86</v>
+        <v>21.31</v>
       </c>
     </row>
     <row r="217">
